--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,225 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129721234</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Limpatjärnsbäcken, Limpatjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>457303</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6675501</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mest troligt vedticka.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129721325</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78741</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Limpatjärnsbäcken, Limpatjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>457264</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6675485</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129721234</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129721325</v>
       </c>
       <c r="B4" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129721234</v>
       </c>
       <c r="B3" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129721325</v>
       </c>
       <c r="B4" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129721234</v>
       </c>
       <c r="B3" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129721234</v>
       </c>
       <c r="B3" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129721234</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129721325</v>
       </c>
       <c r="B4" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129721234</v>
       </c>
       <c r="B3" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129721325</v>
       </c>
       <c r="B4" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129721234</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129721325</v>
       </c>
       <c r="B4" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129721234</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129721325</v>
       </c>
       <c r="B4" t="n">
-        <v>78754</v>
+        <v>78755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 49763-2025 artfynd.xlsx
+++ b/artfynd/A 49763-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69622486</v>
+        <v>129721325</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lagalammshöjden, Dlr</t>
+          <t>Limpatjärnsbäcken, Limpatjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457152.8016088567</v>
+        <v>457264</v>
       </c>
       <c r="R2" t="n">
-        <v>6675808.051204576</v>
+        <v>6675485</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129721234</v>
+        <v>69622486</v>
       </c>
       <c r="B3" t="n">
-        <v>91592</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limpatjärnsbäcken, Limpatjärnsbäcken, Dlr</t>
+          <t>Lagalammshöjden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457303</v>
+        <v>457153</v>
       </c>
       <c r="R3" t="n">
-        <v>6675501</v>
+        <v>6675808</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,34 +847,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mest troligt vedticka.</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -887,44 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129721325</v>
+        <v>129721234</v>
       </c>
       <c r="B4" t="n">
-        <v>78755</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457264</v>
+        <v>457303</v>
       </c>
       <c r="R4" t="n">
-        <v>6675485</v>
+        <v>6675501</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,14 +959,19 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mest troligt vedticka.</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
